--- a/Data/collapsed database manual cases/nayarit_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/nayarit_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AFDF9E-B3A5-6541-A811-DB3C2E8A0BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D754E62-AFF0-8A49-8BFB-DE2EFC0D00C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="401">
   <si>
     <t>uniqueid</t>
   </si>
@@ -1205,6 +1205,27 @@
   </si>
   <si>
     <t>PT</t>
+  </si>
+  <si>
+    <t>PAN_PRI_PRD</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO BARAJAS LOPEZ</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://www.instagram.com/elsanayelipardorivera/%3Fhl%3Den&amp;ved=2ahUKEwjEuobruveSAxXiLEQIHZpdPWcQFnoECCMQAQ&amp;usg=AOvVaw1XzBI2NQG_X6iJbBawhzxP</t>
+  </si>
+  <si>
+    <t>ELSA NAYELI PARDO RIVERA</t>
+  </si>
+  <si>
+    <t>https://pan.org.mx/alcaldes/</t>
+  </si>
+  <si>
+    <t>OLGA LILIA MALDONADO DADO</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://www.facebook.com/elsanayelipardorivera/posts/el-pan-estar%25C3%25A1-bien-representado-me-llena-de-orgullo-ver-a-mi-esposo-y-a-nuestros/1028714639261507/&amp;ved=2ahUKEwinlf7Zzf-SAxV-DkQIHcsQD6IQFnoECDAQAQ&amp;usg=AOvVaw28ucP4Lmj1se2dqpTTbhzZ</t>
   </si>
 </sst>
 </file>
@@ -1558,7 +1579,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S167"/>
+  <dimension ref="A1:S171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -8643,7 +8664,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>18010</v>
       </c>
@@ -8663,7 +8684,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>18013</v>
       </c>
@@ -8683,7 +8704,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>18015</v>
       </c>
@@ -8703,7 +8724,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>18017</v>
       </c>
@@ -8723,7 +8744,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>18018</v>
       </c>
@@ -8743,7 +8764,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>18020</v>
       </c>
@@ -8763,7 +8784,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>18011</v>
       </c>
@@ -8781,6 +8802,80 @@
       </c>
       <c r="I167" t="s">
         <v>392</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>18006</v>
+      </c>
+      <c r="B168">
+        <v>2024</v>
+      </c>
+      <c r="E168" t="s">
+        <v>394</v>
+      </c>
+      <c r="H168" t="s">
+        <v>30</v>
+      </c>
+      <c r="I168" t="s">
+        <v>396</v>
+      </c>
+      <c r="K168" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>18012</v>
+      </c>
+      <c r="B169">
+        <v>2024</v>
+      </c>
+      <c r="E169" t="s">
+        <v>394</v>
+      </c>
+      <c r="F169" t="s">
+        <v>395</v>
+      </c>
+      <c r="H169" t="s">
+        <v>30</v>
+      </c>
+      <c r="I169" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>18006</v>
+      </c>
+      <c r="B170">
+        <v>2024</v>
+      </c>
+      <c r="E170" t="s">
+        <v>394</v>
+      </c>
+      <c r="F170" t="s">
+        <v>399</v>
+      </c>
+      <c r="H170" t="s">
+        <v>30</v>
+      </c>
+      <c r="I170" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>18012</v>
+      </c>
+      <c r="B171">
+        <v>2024</v>
+      </c>
+      <c r="E171" t="s">
+        <v>394</v>
+      </c>
+      <c r="F171" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>
